--- a/data/trans_orig/IP09B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>44867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78541</t>
+          <t>78698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96347</t>
+          <t>95685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21946</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31093</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48733</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34877</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44366</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57778</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50214</t>
+          <t>50449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65406</t>
+          <t>66877</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99514</t>
+          <t>99710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120685</t>
+          <t>120259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>21235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43500</t>
+          <t>43265</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>53046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73791</t>
+          <t>73595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61265</t>
+          <t>60163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25925</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49826</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46517</t>
+          <t>45260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76871</t>
+          <t>76458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102937</t>
+          <t>103352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126768</t>
+          <t>126891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57250</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
